--- a/AAII_Financials/Quarterly/PXDT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PXDT_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="92">
   <si>
     <t>PXDT</t>
   </si>
@@ -656,7 +656,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
@@ -665,39 +665,41 @@
     <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45230</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45046</v>
+      </c>
+      <c r="F7" s="2">
         <v>44865</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>44681</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>44500</v>
       </c>
-      <c r="G7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="I7" s="2" t="s">
         <v>3</v>
       </c>
@@ -707,26 +709,32 @@
       <c r="K7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E8" s="3">
+        <v>4700</v>
+      </c>
+      <c r="F8" s="3">
         <v>1100</v>
       </c>
-      <c r="E8" s="3">
-        <v>4200</v>
-      </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
+        <v>4300</v>
+      </c>
+      <c r="H8" s="3">
         <v>1200</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I8" s="3" t="s">
         <v>3</v>
       </c>
@@ -736,26 +744,32 @@
       <c r="K8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E9" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F9" s="3">
         <v>300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>1400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>500</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I9" s="3" t="s">
         <v>3</v>
       </c>
@@ -765,26 +779,32 @@
       <c r="K9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>3800</v>
+      </c>
+      <c r="F10" s="3">
+        <v>800</v>
+      </c>
+      <c r="G10" s="3">
+        <v>2900</v>
+      </c>
+      <c r="H10" s="3">
         <v>700</v>
       </c>
-      <c r="E10" s="3">
-        <v>2900</v>
-      </c>
-      <c r="F10" s="3">
-        <v>700</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I10" s="3" t="s">
         <v>3</v>
       </c>
@@ -794,8 +814,14 @@
       <c r="K10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -807,25 +833,27 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>2300</v>
+        <v>1900</v>
       </c>
       <c r="E12" s="3">
         <v>4600</v>
       </c>
       <c r="F12" s="3">
-        <v>2400</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>3</v>
+        <v>2300</v>
+      </c>
+      <c r="G12" s="3">
+        <v>4700</v>
+      </c>
+      <c r="H12" s="3">
+        <v>2500</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>3</v>
@@ -836,8 +864,14 @@
       <c r="K12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -865,8 +899,14 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -894,8 +934,14 @@
       <c r="K14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -923,8 +969,14 @@
       <c r="K15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15" s="3">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -933,25 +985,27 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>6800</v>
+        <v>9900</v>
       </c>
       <c r="E17" s="3">
-        <v>11500</v>
+        <v>18100</v>
       </c>
       <c r="F17" s="3">
-        <v>5300</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>3</v>
+        <v>6900</v>
+      </c>
+      <c r="G17" s="3">
+        <v>11700</v>
+      </c>
+      <c r="H17" s="3">
+        <v>5400</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>3</v>
@@ -962,25 +1016,31 @@
       <c r="K17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-5800</v>
+        <v>-7900</v>
       </c>
       <c r="E18" s="3">
-        <v>-7300</v>
+        <v>-13300</v>
       </c>
       <c r="F18" s="3">
-        <v>-4100</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>3</v>
+        <v>-5900</v>
+      </c>
+      <c r="G18" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="H18" s="3">
+        <v>-4200</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>3</v>
@@ -991,8 +1051,14 @@
       <c r="K18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1004,25 +1070,27 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E20" s="3">
+        <v>300</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>100</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
+      <c r="H20" s="3">
+        <v>0</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>3</v>
@@ -1033,26 +1101,32 @@
       <c r="K20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-5500</v>
+        <v>-7000</v>
       </c>
       <c r="E21" s="3">
-        <v>-6700</v>
+        <v>-12300</v>
       </c>
       <c r="F21" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="G21" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="H21" s="3">
         <v>-3900</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1062,8 +1136,14 @@
       <c r="K21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1076,11 +1156,11 @@
       <c r="F22" s="3">
         <v>100</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
+      <c r="G22" s="3">
+        <v>200</v>
+      </c>
+      <c r="H22" s="3">
+        <v>100</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>3</v>
@@ -1091,25 +1171,31 @@
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-5900</v>
+        <v>-7800</v>
       </c>
       <c r="E23" s="3">
-        <v>-7400</v>
+        <v>-13200</v>
       </c>
       <c r="F23" s="3">
-        <v>-4100</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>3</v>
+        <v>-6000</v>
+      </c>
+      <c r="G23" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="H23" s="3">
+        <v>-4200</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>3</v>
@@ -1120,8 +1206,14 @@
       <c r="K23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1149,8 +1241,14 @@
       <c r="K24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1178,25 +1276,31 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-5900</v>
+        <v>-7800</v>
       </c>
       <c r="E26" s="3">
-        <v>-7400</v>
+        <v>-13200</v>
       </c>
       <c r="F26" s="3">
-        <v>-4100</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>3</v>
+        <v>-6000</v>
+      </c>
+      <c r="G26" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="H26" s="3">
+        <v>-4200</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>3</v>
@@ -1207,25 +1311,31 @@
       <c r="K26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-5900</v>
+        <v>-7800</v>
       </c>
       <c r="E27" s="3">
-        <v>-7400</v>
+        <v>-13200</v>
       </c>
       <c r="F27" s="3">
-        <v>-4100</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>3</v>
+        <v>-6000</v>
+      </c>
+      <c r="G27" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="H27" s="3">
+        <v>-4200</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>3</v>
@@ -1236,8 +1346,14 @@
       <c r="K27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1265,8 +1381,14 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1294,8 +1416,14 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1323,8 +1451,14 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1352,25 +1486,31 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="E32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>-100</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
+      <c r="H32" s="3">
+        <v>0</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>3</v>
@@ -1381,25 +1521,31 @@
       <c r="K32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-5900</v>
+        <v>-7800</v>
       </c>
       <c r="E33" s="3">
-        <v>-7400</v>
+        <v>-13200</v>
       </c>
       <c r="F33" s="3">
-        <v>-4100</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>3</v>
+        <v>-6000</v>
+      </c>
+      <c r="G33" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="H33" s="3">
+        <v>-4200</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>3</v>
@@ -1410,8 +1556,14 @@
       <c r="K33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1439,25 +1591,31 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-5900</v>
+        <v>-7800</v>
       </c>
       <c r="E35" s="3">
-        <v>-7400</v>
+        <v>-13200</v>
       </c>
       <c r="F35" s="3">
-        <v>-4100</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>3</v>
+        <v>-6000</v>
+      </c>
+      <c r="G35" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="H35" s="3">
+        <v>-4200</v>
       </c>
       <c r="I35" s="3" t="s">
         <v>3</v>
@@ -1468,31 +1626,37 @@
       <c r="K35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45230</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45046</v>
+      </c>
+      <c r="F38" s="2">
         <v>44865</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>44681</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>44500</v>
       </c>
-      <c r="G38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="I38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1502,8 +1666,14 @@
       <c r="K38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1515,8 +1685,10 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1528,19 +1700,21 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>21700</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>3</v>
+        <v>16300</v>
+      </c>
+      <c r="E41" s="3">
+        <v>14400</v>
+      </c>
+      <c r="F41" s="3">
+        <v>22100</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>3</v>
@@ -1557,8 +1731,14 @@
       <c r="K41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1586,20 +1766,26 @@
       <c r="K42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>100</v>
+      </c>
+      <c r="E43" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F43" s="3">
         <v>800</v>
       </c>
-      <c r="E43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1615,20 +1801,26 @@
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E44" s="3">
+        <v>800</v>
+      </c>
+      <c r="F44" s="3">
         <v>400</v>
       </c>
-      <c r="E44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G44" s="3" t="s">
         <v>3</v>
       </c>
@@ -1644,20 +1836,26 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E45" s="3">
+        <v>4000</v>
+      </c>
+      <c r="F45" s="3">
         <v>1900</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G45" s="3" t="s">
         <v>3</v>
       </c>
@@ -1673,19 +1871,25 @@
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>24800</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>3</v>
+        <v>20000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>20500</v>
+      </c>
+      <c r="F46" s="3">
+        <v>25200</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>3</v>
@@ -1702,8 +1906,14 @@
       <c r="K46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1731,19 +1941,25 @@
       <c r="K47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L47" s="3">
+        <v>0</v>
+      </c>
+      <c r="M47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>10300</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>3</v>
+        <v>6400</v>
+      </c>
+      <c r="E48" s="3">
+        <v>3700</v>
+      </c>
+      <c r="F48" s="3">
+        <v>10500</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>3</v>
@@ -1760,20 +1976,26 @@
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>100</v>
+      </c>
+      <c r="E49" s="3">
+        <v>100</v>
+      </c>
+      <c r="F49" s="3">
         <v>800</v>
       </c>
-      <c r="E49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G49" s="3" t="s">
         <v>3</v>
       </c>
@@ -1789,8 +2011,14 @@
       <c r="K49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1818,8 +2046,14 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1847,37 +2081,49 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E52" s="3">
-        <v>0</v>
-      </c>
-      <c r="F52" s="3">
-        <v>0</v>
-      </c>
-      <c r="G52" s="3">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3">
-        <v>0</v>
-      </c>
-      <c r="I52" s="3">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3">
-        <v>0</v>
+        <v>700</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L52" s="3">
+        <v>0</v>
+      </c>
+      <c r="M52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1905,19 +2151,25 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>35900</v>
-      </c>
-      <c r="E54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>3</v>
+        <v>27500</v>
+      </c>
+      <c r="E54" s="3">
+        <v>25100</v>
+      </c>
+      <c r="F54" s="3">
+        <v>36500</v>
       </c>
       <c r="G54" s="3" t="s">
         <v>3</v>
@@ -1934,8 +2186,14 @@
       <c r="K54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1947,8 +2205,10 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1960,19 +2220,21 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>900</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>3</v>
+        <v>1100</v>
+      </c>
+      <c r="E57" s="3">
+        <v>3700</v>
+      </c>
+      <c r="F57" s="3">
+        <v>1000</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>3</v>
@@ -1989,20 +2251,26 @@
       <c r="K57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E58" s="3">
+        <v>6900</v>
+      </c>
+      <c r="F58" s="3">
         <v>200</v>
       </c>
-      <c r="E58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2018,20 +2286,26 @@
       <c r="K58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E59" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F59" s="3">
         <v>1400</v>
       </c>
-      <c r="E59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2047,20 +2321,26 @@
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E60" s="3">
+        <v>11900</v>
+      </c>
+      <c r="F60" s="3">
         <v>2500</v>
       </c>
-      <c r="E60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2076,19 +2356,25 @@
       <c r="K60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>7000</v>
+        <v>100</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>7100</v>
       </c>
       <c r="G61" s="3">
         <v>0</v>
@@ -2105,19 +2391,25 @@
       <c r="K61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>6600</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>3</v>
+        <v>3200</v>
+      </c>
+      <c r="E62" s="3">
+        <v>0</v>
+      </c>
+      <c r="F62" s="3">
+        <v>6700</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>3</v>
@@ -2134,8 +2426,14 @@
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2163,8 +2461,14 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2192,8 +2496,14 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2221,19 +2531,25 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>16100</v>
-      </c>
-      <c r="E66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>3</v>
+        <v>12500</v>
+      </c>
+      <c r="E66" s="3">
+        <v>12300</v>
+      </c>
+      <c r="F66" s="3">
+        <v>16400</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>3</v>
@@ -2250,8 +2566,14 @@
       <c r="K66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2263,8 +2585,10 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2292,8 +2616,14 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2321,19 +2651,25 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>7200</v>
+        <v>0</v>
       </c>
       <c r="E70" s="3">
         <v>0</v>
       </c>
       <c r="F70" s="3">
-        <v>0</v>
+        <v>7300</v>
       </c>
       <c r="G70" s="3">
         <v>0</v>
@@ -2350,8 +2686,14 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2379,19 +2721,25 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-21900</v>
-      </c>
-      <c r="E72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>3</v>
+        <v>-37300</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-29500</v>
+      </c>
+      <c r="F72" s="3">
+        <v>-22300</v>
       </c>
       <c r="G72" s="3" t="s">
         <v>3</v>
@@ -2408,8 +2756,14 @@
       <c r="K72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2437,8 +2791,14 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2466,8 +2826,14 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2495,19 +2861,25 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>12500</v>
-      </c>
-      <c r="E76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F76" s="3" t="s">
-        <v>3</v>
+        <v>15000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>12800</v>
+      </c>
+      <c r="F76" s="3">
+        <v>12700</v>
       </c>
       <c r="G76" s="3" t="s">
         <v>3</v>
@@ -2524,8 +2896,14 @@
       <c r="K76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2553,31 +2931,37 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45230</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45046</v>
+      </c>
+      <c r="F80" s="2">
         <v>44865</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>44681</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>44500</v>
       </c>
-      <c r="G80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="H80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="I80" s="2" t="s">
         <v>3</v>
       </c>
@@ -2587,25 +2971,31 @@
       <c r="K80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-5900</v>
+        <v>-7800</v>
       </c>
       <c r="E81" s="3">
-        <v>-7400</v>
+        <v>-13200</v>
       </c>
       <c r="F81" s="3">
-        <v>-4100</v>
-      </c>
-      <c r="G81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H81" s="3" t="s">
-        <v>3</v>
+        <v>-6000</v>
+      </c>
+      <c r="G81" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="H81" s="3">
+        <v>-4200</v>
       </c>
       <c r="I81" s="3" t="s">
         <v>3</v>
@@ -2616,8 +3006,14 @@
       <c r="K81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2629,26 +3025,28 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>700</v>
+      </c>
+      <c r="E83" s="3">
+        <v>700</v>
+      </c>
+      <c r="F83" s="3">
         <v>300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>200</v>
       </c>
-      <c r="G83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I83" s="3" t="s">
         <v>3</v>
       </c>
@@ -2658,8 +3056,14 @@
       <c r="K83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2687,8 +3091,14 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2716,8 +3126,14 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2745,8 +3161,14 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2774,8 +3196,14 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2803,25 +3231,31 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-5700</v>
+        <v>-9300</v>
       </c>
       <c r="E89" s="3">
-        <v>-7100</v>
+        <v>-12200</v>
       </c>
       <c r="F89" s="3">
-        <v>-4500</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>3</v>
+        <v>-5800</v>
+      </c>
+      <c r="G89" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="H89" s="3">
+        <v>-4600</v>
       </c>
       <c r="I89" s="3" t="s">
         <v>3</v>
@@ -2832,8 +3266,14 @@
       <c r="K89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2845,23 +3285,25 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-68800</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-40000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-49300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-12100</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
       <c r="H91" s="3">
         <v>0</v>
       </c>
@@ -2874,8 +3316,14 @@
       <c r="K91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2903,8 +3351,14 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2932,26 +3386,32 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-600</v>
+      </c>
+      <c r="F94" s="3">
         <v>-300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-400</v>
       </c>
-      <c r="G94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I94" s="3" t="s">
         <v>3</v>
       </c>
@@ -2961,8 +3421,14 @@
       <c r="K94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2974,8 +3440,10 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3003,8 +3471,14 @@
       <c r="K96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3032,8 +3506,14 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3061,8 +3541,14 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3090,25 +3576,31 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>15900</v>
+        <v>11400</v>
       </c>
       <c r="E100" s="3">
+        <v>15100</v>
+      </c>
+      <c r="F100" s="3">
+        <v>16100</v>
+      </c>
+      <c r="G100" s="3">
         <v>-800</v>
       </c>
-      <c r="F100" s="3">
-        <v>1500</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
+      <c r="H100" s="3">
+        <v>1600</v>
       </c>
       <c r="I100" s="3" t="s">
         <v>3</v>
@@ -3119,54 +3611,66 @@
       <c r="K100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+        <v>300</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>9800</v>
+        <v>1900</v>
       </c>
       <c r="E102" s="3">
-        <v>-8400</v>
+        <v>2300</v>
       </c>
       <c r="F102" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="G102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>3</v>
+        <v>10000</v>
+      </c>
+      <c r="G102" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="H102" s="3">
+        <v>-3500</v>
       </c>
       <c r="I102" s="3" t="s">
         <v>3</v>
@@ -3175,6 +3679,12 @@
         <v>3</v>
       </c>
       <c r="K102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PXDT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PXDT_QTR_FIN.xlsx
@@ -721,19 +721,19 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>2000</v>
+        <v>1900</v>
       </c>
       <c r="E8" s="3">
-        <v>4700</v>
+        <v>4500</v>
       </c>
       <c r="F8" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G8" s="3">
+        <v>4100</v>
+      </c>
+      <c r="H8" s="3">
         <v>1100</v>
-      </c>
-      <c r="G8" s="3">
-        <v>4300</v>
-      </c>
-      <c r="H8" s="3">
-        <v>1200</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>3</v>
@@ -756,16 +756,16 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="E9" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="F9" s="3">
         <v>300</v>
       </c>
       <c r="G9" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="H9" s="3">
         <v>500</v>
@@ -794,13 +794,13 @@
         <v>1000</v>
       </c>
       <c r="E10" s="3">
-        <v>3800</v>
+        <v>3600</v>
       </c>
       <c r="F10" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="G10" s="3">
-        <v>2900</v>
+        <v>2700</v>
       </c>
       <c r="H10" s="3">
         <v>700</v>
@@ -841,19 +841,19 @@
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>1900</v>
+        <v>1800</v>
       </c>
       <c r="E12" s="3">
-        <v>4600</v>
+        <v>4400</v>
       </c>
       <c r="F12" s="3">
+        <v>2200</v>
+      </c>
+      <c r="G12" s="3">
+        <v>4400</v>
+      </c>
+      <c r="H12" s="3">
         <v>2300</v>
-      </c>
-      <c r="G12" s="3">
-        <v>4700</v>
-      </c>
-      <c r="H12" s="3">
-        <v>2500</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>3</v>
@@ -993,19 +993,19 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>9900</v>
+        <v>9400</v>
       </c>
       <c r="E17" s="3">
-        <v>18100</v>
+        <v>17100</v>
       </c>
       <c r="F17" s="3">
-        <v>6900</v>
+        <v>6600</v>
       </c>
       <c r="G17" s="3">
-        <v>11700</v>
+        <v>11100</v>
       </c>
       <c r="H17" s="3">
-        <v>5400</v>
+        <v>5100</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>3</v>
@@ -1028,19 +1028,19 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-7900</v>
+        <v>-7500</v>
       </c>
       <c r="E18" s="3">
-        <v>-13300</v>
+        <v>-12600</v>
       </c>
       <c r="F18" s="3">
-        <v>-5900</v>
+        <v>-5600</v>
       </c>
       <c r="G18" s="3">
-        <v>-7400</v>
+        <v>-7000</v>
       </c>
       <c r="H18" s="3">
-        <v>-4200</v>
+        <v>-3900</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>3</v>
@@ -1113,19 +1113,19 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-7000</v>
+        <v>-6600</v>
       </c>
       <c r="E21" s="3">
-        <v>-12300</v>
+        <v>-11700</v>
       </c>
       <c r="F21" s="3">
-        <v>-5600</v>
+        <v>-5300</v>
       </c>
       <c r="G21" s="3">
-        <v>-6800</v>
+        <v>-6400</v>
       </c>
       <c r="H21" s="3">
-        <v>-3900</v>
+        <v>-3700</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>3</v>
@@ -1183,19 +1183,19 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-7800</v>
+        <v>-7300</v>
       </c>
       <c r="E23" s="3">
-        <v>-13200</v>
+        <v>-12500</v>
       </c>
       <c r="F23" s="3">
-        <v>-6000</v>
+        <v>-5600</v>
       </c>
       <c r="G23" s="3">
-        <v>-7500</v>
+        <v>-7100</v>
       </c>
       <c r="H23" s="3">
-        <v>-4200</v>
+        <v>-4000</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>3</v>
@@ -1288,19 +1288,19 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-7800</v>
+        <v>-7300</v>
       </c>
       <c r="E26" s="3">
-        <v>-13200</v>
+        <v>-12500</v>
       </c>
       <c r="F26" s="3">
-        <v>-6000</v>
+        <v>-5600</v>
       </c>
       <c r="G26" s="3">
-        <v>-7500</v>
+        <v>-7100</v>
       </c>
       <c r="H26" s="3">
-        <v>-4200</v>
+        <v>-4000</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>3</v>
@@ -1323,19 +1323,19 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-7800</v>
+        <v>-7300</v>
       </c>
       <c r="E27" s="3">
-        <v>-13200</v>
+        <v>-12500</v>
       </c>
       <c r="F27" s="3">
-        <v>-6000</v>
+        <v>-5600</v>
       </c>
       <c r="G27" s="3">
-        <v>-7500</v>
+        <v>-7100</v>
       </c>
       <c r="H27" s="3">
-        <v>-4200</v>
+        <v>-4000</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>3</v>
@@ -1533,19 +1533,19 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-7800</v>
+        <v>-7300</v>
       </c>
       <c r="E33" s="3">
-        <v>-13200</v>
+        <v>-12500</v>
       </c>
       <c r="F33" s="3">
-        <v>-6000</v>
+        <v>-5600</v>
       </c>
       <c r="G33" s="3">
-        <v>-7500</v>
+        <v>-7100</v>
       </c>
       <c r="H33" s="3">
-        <v>-4200</v>
+        <v>-4000</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>3</v>
@@ -1603,19 +1603,19 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-7800</v>
+        <v>-7300</v>
       </c>
       <c r="E35" s="3">
-        <v>-13200</v>
+        <v>-12500</v>
       </c>
       <c r="F35" s="3">
-        <v>-6000</v>
+        <v>-5600</v>
       </c>
       <c r="G35" s="3">
-        <v>-7500</v>
+        <v>-7100</v>
       </c>
       <c r="H35" s="3">
-        <v>-4200</v>
+        <v>-4000</v>
       </c>
       <c r="I35" s="3" t="s">
         <v>3</v>
@@ -1708,13 +1708,13 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>16300</v>
+        <v>15400</v>
       </c>
       <c r="E41" s="3">
-        <v>14400</v>
+        <v>13600</v>
       </c>
       <c r="F41" s="3">
-        <v>22100</v>
+        <v>20900</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>3</v>
@@ -1813,13 +1813,13 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="E44" s="3">
         <v>800</v>
       </c>
       <c r="F44" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>3</v>
@@ -1848,13 +1848,13 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>2400</v>
+        <v>2300</v>
       </c>
       <c r="E45" s="3">
-        <v>4000</v>
+        <v>3700</v>
       </c>
       <c r="F45" s="3">
-        <v>1900</v>
+        <v>1800</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>3</v>
@@ -1883,13 +1883,13 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>20000</v>
+        <v>18900</v>
       </c>
       <c r="E46" s="3">
-        <v>20500</v>
+        <v>19400</v>
       </c>
       <c r="F46" s="3">
-        <v>25200</v>
+        <v>23800</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>3</v>
@@ -1953,13 +1953,13 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>6400</v>
+        <v>6100</v>
       </c>
       <c r="E48" s="3">
-        <v>3700</v>
+        <v>3500</v>
       </c>
       <c r="F48" s="3">
-        <v>10500</v>
+        <v>9900</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>3</v>
@@ -2093,7 +2093,7 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="E52" s="3">
         <v>700</v>
@@ -2163,13 +2163,13 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>27500</v>
+        <v>26000</v>
       </c>
       <c r="E54" s="3">
-        <v>25100</v>
+        <v>23700</v>
       </c>
       <c r="F54" s="3">
-        <v>36500</v>
+        <v>34500</v>
       </c>
       <c r="G54" s="3" t="s">
         <v>3</v>
@@ -2228,13 +2228,13 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="E57" s="3">
-        <v>3700</v>
+        <v>3500</v>
       </c>
       <c r="F57" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>3</v>
@@ -2263,10 +2263,10 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>6800</v>
+        <v>6500</v>
       </c>
       <c r="E58" s="3">
-        <v>6900</v>
+        <v>6600</v>
       </c>
       <c r="F58" s="3">
         <v>200</v>
@@ -2298,13 +2298,13 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E59" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F59" s="3">
         <v>1300</v>
-      </c>
-      <c r="E59" s="3">
-        <v>1300</v>
-      </c>
-      <c r="F59" s="3">
-        <v>1400</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>3</v>
@@ -2333,13 +2333,13 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>9200</v>
+        <v>8700</v>
       </c>
       <c r="E60" s="3">
-        <v>11900</v>
+        <v>11300</v>
       </c>
       <c r="F60" s="3">
-        <v>2500</v>
+        <v>2400</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>3</v>
@@ -2374,7 +2374,7 @@
         <v>300</v>
       </c>
       <c r="F61" s="3">
-        <v>7100</v>
+        <v>6800</v>
       </c>
       <c r="G61" s="3">
         <v>0</v>
@@ -2403,13 +2403,13 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>3200</v>
+        <v>3000</v>
       </c>
       <c r="E62" s="3">
         <v>0</v>
       </c>
       <c r="F62" s="3">
-        <v>6700</v>
+        <v>6400</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>3</v>
@@ -2543,13 +2543,13 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>12500</v>
+        <v>11800</v>
       </c>
       <c r="E66" s="3">
-        <v>12300</v>
+        <v>11600</v>
       </c>
       <c r="F66" s="3">
-        <v>16400</v>
+        <v>15500</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>3</v>
@@ -2669,7 +2669,7 @@
         <v>0</v>
       </c>
       <c r="F70" s="3">
-        <v>7300</v>
+        <v>7000</v>
       </c>
       <c r="G70" s="3">
         <v>0</v>
@@ -2733,13 +2733,13 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-37300</v>
+        <v>-35300</v>
       </c>
       <c r="E72" s="3">
-        <v>-29500</v>
+        <v>-28000</v>
       </c>
       <c r="F72" s="3">
-        <v>-22300</v>
+        <v>-21100</v>
       </c>
       <c r="G72" s="3" t="s">
         <v>3</v>
@@ -2873,13 +2873,13 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>15000</v>
+        <v>14200</v>
       </c>
       <c r="E76" s="3">
-        <v>12800</v>
+        <v>12100</v>
       </c>
       <c r="F76" s="3">
-        <v>12700</v>
+        <v>12100</v>
       </c>
       <c r="G76" s="3" t="s">
         <v>3</v>
@@ -2983,19 +2983,19 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-7800</v>
+        <v>-7300</v>
       </c>
       <c r="E81" s="3">
-        <v>-13200</v>
+        <v>-12500</v>
       </c>
       <c r="F81" s="3">
-        <v>-6000</v>
+        <v>-5600</v>
       </c>
       <c r="G81" s="3">
-        <v>-7500</v>
+        <v>-7100</v>
       </c>
       <c r="H81" s="3">
-        <v>-4200</v>
+        <v>-4000</v>
       </c>
       <c r="I81" s="3" t="s">
         <v>3</v>
@@ -3033,13 +3033,13 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="E83" s="3">
         <v>700</v>
       </c>
       <c r="F83" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G83" s="3">
         <v>500</v>
@@ -3243,19 +3243,19 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-9300</v>
+        <v>-8800</v>
       </c>
       <c r="E89" s="3">
-        <v>-12200</v>
+        <v>-11600</v>
       </c>
       <c r="F89" s="3">
-        <v>-5800</v>
+        <v>-5500</v>
       </c>
       <c r="G89" s="3">
-        <v>-7200</v>
+        <v>-6900</v>
       </c>
       <c r="H89" s="3">
-        <v>-4600</v>
+        <v>-4300</v>
       </c>
       <c r="I89" s="3" t="s">
         <v>3</v>
@@ -3398,7 +3398,7 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-500</v>
+        <v>-400</v>
       </c>
       <c r="E94" s="3">
         <v>-600</v>
@@ -3588,19 +3588,19 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>11400</v>
+        <v>10800</v>
       </c>
       <c r="E100" s="3">
-        <v>15100</v>
+        <v>14300</v>
       </c>
       <c r="F100" s="3">
-        <v>16100</v>
+        <v>15200</v>
       </c>
       <c r="G100" s="3">
         <v>-800</v>
       </c>
       <c r="H100" s="3">
-        <v>1600</v>
+        <v>1500</v>
       </c>
       <c r="I100" s="3" t="s">
         <v>3</v>
@@ -3658,19 +3658,19 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>1900</v>
+        <v>1800</v>
       </c>
       <c r="E102" s="3">
-        <v>2300</v>
+        <v>2200</v>
       </c>
       <c r="F102" s="3">
-        <v>10000</v>
+        <v>9400</v>
       </c>
       <c r="G102" s="3">
-        <v>-8600</v>
+        <v>-8100</v>
       </c>
       <c r="H102" s="3">
-        <v>-3500</v>
+        <v>-3300</v>
       </c>
       <c r="I102" s="3" t="s">
         <v>3</v>

--- a/AAII_Financials/Quarterly/PXDT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PXDT_QTR_FIN.xlsx
@@ -656,53 +656,54 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45412</v>
+      </c>
+      <c r="E7" s="2">
         <v>45230</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45046</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44865</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44681</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44500</v>
       </c>
-      <c r="I7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="J7" s="2" t="s">
         <v>3</v>
       </c>
@@ -715,28 +716,31 @@
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>1900</v>
+        <v>7100</v>
       </c>
       <c r="E8" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F8" s="3">
+        <v>5000</v>
+      </c>
+      <c r="G8" s="3">
+        <v>1100</v>
+      </c>
+      <c r="H8" s="3">
         <v>4500</v>
       </c>
-      <c r="F8" s="3">
-        <v>1000</v>
-      </c>
-      <c r="G8" s="3">
-        <v>4100</v>
-      </c>
-      <c r="H8" s="3">
-        <v>1100</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
+      <c r="I8" s="3">
+        <v>1300</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>3</v>
@@ -750,29 +754,32 @@
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>900</v>
+        <v>2400</v>
       </c>
       <c r="E9" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="F9" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G9" s="3">
         <v>300</v>
       </c>
-      <c r="G9" s="3">
-        <v>1300</v>
-      </c>
       <c r="H9" s="3">
+        <v>1500</v>
+      </c>
+      <c r="I9" s="3">
         <v>500</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J9" s="3" t="s">
         <v>3</v>
       </c>
@@ -785,28 +792,31 @@
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>1000</v>
+        <v>4700</v>
       </c>
       <c r="E10" s="3">
-        <v>3600</v>
+        <v>1100</v>
       </c>
       <c r="F10" s="3">
-        <v>700</v>
+        <v>4000</v>
       </c>
       <c r="G10" s="3">
-        <v>2700</v>
+        <v>800</v>
       </c>
       <c r="H10" s="3">
-        <v>700</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
+        <v>3100</v>
+      </c>
+      <c r="I10" s="3">
+        <v>800</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>3</v>
@@ -820,8 +830,11 @@
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -835,28 +848,29 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>1800</v>
+        <v>3600</v>
       </c>
       <c r="E12" s="3">
-        <v>4400</v>
+        <v>2000</v>
       </c>
       <c r="F12" s="3">
-        <v>2200</v>
+        <v>4900</v>
       </c>
       <c r="G12" s="3">
-        <v>4400</v>
+        <v>2400</v>
       </c>
       <c r="H12" s="3">
-        <v>2300</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>3</v>
+        <v>4900</v>
+      </c>
+      <c r="I12" s="3">
+        <v>2600</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>3</v>
@@ -870,8 +884,11 @@
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -905,8 +922,11 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -940,8 +960,11 @@
       <c r="M14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -975,8 +998,11 @@
       <c r="M15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -987,28 +1013,29 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>9400</v>
+        <v>21300</v>
       </c>
       <c r="E17" s="3">
-        <v>17100</v>
+        <v>10500</v>
       </c>
       <c r="F17" s="3">
-        <v>6600</v>
+        <v>19100</v>
       </c>
       <c r="G17" s="3">
-        <v>11100</v>
+        <v>7300</v>
       </c>
       <c r="H17" s="3">
-        <v>5100</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>3</v>
+        <v>12300</v>
+      </c>
+      <c r="I17" s="3">
+        <v>5700</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>3</v>
@@ -1022,28 +1049,31 @@
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-7500</v>
+        <v>-14300</v>
       </c>
       <c r="E18" s="3">
-        <v>-12600</v>
+        <v>-8300</v>
       </c>
       <c r="F18" s="3">
-        <v>-5600</v>
+        <v>-14100</v>
       </c>
       <c r="G18" s="3">
-        <v>-7000</v>
+        <v>-6200</v>
       </c>
       <c r="H18" s="3">
-        <v>-3900</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>3</v>
+        <v>-7800</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-4400</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>3</v>
@@ -1057,8 +1087,11 @@
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1072,28 +1105,29 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="E20" s="3">
         <v>300</v>
       </c>
       <c r="F20" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>100</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
+      <c r="I20" s="3">
+        <v>0</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>3</v>
@@ -1107,28 +1141,31 @@
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-6600</v>
+        <v>-12400</v>
       </c>
       <c r="E21" s="3">
-        <v>-11700</v>
+        <v>-7300</v>
       </c>
       <c r="F21" s="3">
-        <v>-5300</v>
+        <v>-13000</v>
       </c>
       <c r="G21" s="3">
-        <v>-6400</v>
+        <v>-5900</v>
       </c>
       <c r="H21" s="3">
-        <v>-3700</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
+        <v>-7200</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-4100</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>3</v>
@@ -1142,29 +1179,32 @@
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>200</v>
+      </c>
+      <c r="E22" s="3">
         <v>100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>100</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1177,28 +1217,31 @@
       <c r="M22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-7300</v>
+        <v>-14000</v>
       </c>
       <c r="E23" s="3">
-        <v>-12500</v>
+        <v>-8200</v>
       </c>
       <c r="F23" s="3">
-        <v>-5600</v>
+        <v>-14000</v>
       </c>
       <c r="G23" s="3">
-        <v>-7100</v>
+        <v>-6300</v>
       </c>
       <c r="H23" s="3">
-        <v>-4000</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>3</v>
+        <v>-7900</v>
+      </c>
+      <c r="I23" s="3">
+        <v>-4400</v>
       </c>
       <c r="J23" s="3" t="s">
         <v>3</v>
@@ -1212,8 +1255,11 @@
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1247,8 +1293,11 @@
       <c r="M24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1282,28 +1331,31 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-7300</v>
+        <v>-14000</v>
       </c>
       <c r="E26" s="3">
-        <v>-12500</v>
+        <v>-8200</v>
       </c>
       <c r="F26" s="3">
-        <v>-5600</v>
+        <v>-14000</v>
       </c>
       <c r="G26" s="3">
-        <v>-7100</v>
+        <v>-6300</v>
       </c>
       <c r="H26" s="3">
-        <v>-4000</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>3</v>
+        <v>-7900</v>
+      </c>
+      <c r="I26" s="3">
+        <v>-4400</v>
       </c>
       <c r="J26" s="3" t="s">
         <v>3</v>
@@ -1317,28 +1369,31 @@
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-7300</v>
+        <v>-14000</v>
       </c>
       <c r="E27" s="3">
-        <v>-12500</v>
+        <v>-8200</v>
       </c>
       <c r="F27" s="3">
-        <v>-5600</v>
+        <v>-14000</v>
       </c>
       <c r="G27" s="3">
-        <v>-7100</v>
+        <v>-6300</v>
       </c>
       <c r="H27" s="3">
-        <v>-4000</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>3</v>
+        <v>-7900</v>
+      </c>
+      <c r="I27" s="3">
+        <v>-4400</v>
       </c>
       <c r="J27" s="3" t="s">
         <v>3</v>
@@ -1352,8 +1407,11 @@
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1387,8 +1445,11 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1422,8 +1483,11 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1457,8 +1521,11 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1492,28 +1559,31 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-300</v>
+        <v>-500</v>
       </c>
       <c r="E32" s="3">
         <v>-300</v>
       </c>
       <c r="F32" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>-100</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
+      <c r="I32" s="3">
+        <v>0</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>3</v>
@@ -1527,28 +1597,31 @@
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-7300</v>
+        <v>-14000</v>
       </c>
       <c r="E33" s="3">
-        <v>-12500</v>
+        <v>-8200</v>
       </c>
       <c r="F33" s="3">
-        <v>-5600</v>
+        <v>-14000</v>
       </c>
       <c r="G33" s="3">
-        <v>-7100</v>
+        <v>-6300</v>
       </c>
       <c r="H33" s="3">
-        <v>-4000</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>3</v>
+        <v>-7900</v>
+      </c>
+      <c r="I33" s="3">
+        <v>-4400</v>
       </c>
       <c r="J33" s="3" t="s">
         <v>3</v>
@@ -1562,8 +1635,11 @@
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1597,28 +1673,31 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-7300</v>
+        <v>-14000</v>
       </c>
       <c r="E35" s="3">
-        <v>-12500</v>
+        <v>-8200</v>
       </c>
       <c r="F35" s="3">
-        <v>-5600</v>
+        <v>-14000</v>
       </c>
       <c r="G35" s="3">
-        <v>-7100</v>
+        <v>-6300</v>
       </c>
       <c r="H35" s="3">
-        <v>-4000</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>3</v>
+        <v>-7900</v>
+      </c>
+      <c r="I35" s="3">
+        <v>-4400</v>
       </c>
       <c r="J35" s="3" t="s">
         <v>3</v>
@@ -1632,34 +1711,37 @@
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45412</v>
+      </c>
+      <c r="E38" s="2">
         <v>45230</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45046</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44865</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44681</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44500</v>
       </c>
-      <c r="I38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="J38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1672,8 +1754,11 @@
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1687,8 +1772,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1702,22 +1788,23 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>15400</v>
+        <v>11400</v>
       </c>
       <c r="E41" s="3">
-        <v>13600</v>
+        <v>17200</v>
       </c>
       <c r="F41" s="3">
-        <v>20900</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>3</v>
+        <v>15200</v>
+      </c>
+      <c r="G41" s="3">
+        <v>23300</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>3</v>
@@ -1737,8 +1824,11 @@
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1772,22 +1862,25 @@
       <c r="M42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E43" s="3">
         <v>100</v>
       </c>
-      <c r="E43" s="3">
-        <v>1300</v>
-      </c>
       <c r="F43" s="3">
-        <v>800</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>3</v>
+        <v>1400</v>
+      </c>
+      <c r="G43" s="3">
+        <v>900</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>3</v>
@@ -1807,8 +1900,11 @@
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1816,13 +1912,13 @@
         <v>1100</v>
       </c>
       <c r="E44" s="3">
-        <v>800</v>
+        <v>1300</v>
       </c>
       <c r="F44" s="3">
-        <v>300</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>3</v>
+        <v>900</v>
+      </c>
+      <c r="G44" s="3">
+        <v>400</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>3</v>
@@ -1842,22 +1938,25 @@
       <c r="M44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>2300</v>
+        <v>700</v>
       </c>
       <c r="E45" s="3">
-        <v>3700</v>
+        <v>2500</v>
       </c>
       <c r="F45" s="3">
-        <v>1800</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>3</v>
+        <v>4200</v>
+      </c>
+      <c r="G45" s="3">
+        <v>2000</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>3</v>
@@ -1877,22 +1976,25 @@
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>18900</v>
+        <v>15900</v>
       </c>
       <c r="E46" s="3">
-        <v>19400</v>
+        <v>21100</v>
       </c>
       <c r="F46" s="3">
-        <v>23800</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>3</v>
+        <v>21600</v>
+      </c>
+      <c r="G46" s="3">
+        <v>26500</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>3</v>
@@ -1912,8 +2014,11 @@
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1947,22 +2052,25 @@
       <c r="M47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>6100</v>
+        <v>7000</v>
       </c>
       <c r="E48" s="3">
-        <v>3500</v>
+        <v>6800</v>
       </c>
       <c r="F48" s="3">
-        <v>9900</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>3</v>
+        <v>3900</v>
+      </c>
+      <c r="G48" s="3">
+        <v>11100</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>3</v>
@@ -1982,8 +2090,11 @@
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -1994,11 +2105,11 @@
         <v>100</v>
       </c>
       <c r="F49" s="3">
+        <v>100</v>
+      </c>
+      <c r="G49" s="3">
         <v>800</v>
       </c>
-      <c r="G49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2017,8 +2128,11 @@
       <c r="M49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2052,8 +2166,11 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2087,20 +2204,23 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="E52" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F52" s="3">
         <v>700</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2113,8 +2233,8 @@
       <c r="J52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
+      <c r="K52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L52" s="3">
         <v>0</v>
@@ -2122,8 +2242,11 @@
       <c r="M52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2157,22 +2280,25 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>26000</v>
+        <v>24000</v>
       </c>
       <c r="E54" s="3">
-        <v>23700</v>
+        <v>29000</v>
       </c>
       <c r="F54" s="3">
-        <v>34500</v>
-      </c>
-      <c r="G54" s="3" t="s">
-        <v>3</v>
+        <v>26400</v>
+      </c>
+      <c r="G54" s="3">
+        <v>38400</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>3</v>
@@ -2192,8 +2318,11 @@
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2207,8 +2336,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2222,23 +2352,24 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E57" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F57" s="3">
+        <v>3900</v>
+      </c>
+      <c r="G57" s="3">
         <v>1000</v>
       </c>
-      <c r="E57" s="3">
-        <v>3500</v>
-      </c>
-      <c r="F57" s="3">
-        <v>900</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2257,23 +2388,26 @@
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>6500</v>
+        <v>100</v>
       </c>
       <c r="E58" s="3">
-        <v>6600</v>
+        <v>7200</v>
       </c>
       <c r="F58" s="3">
+        <v>7300</v>
+      </c>
+      <c r="G58" s="3">
         <v>200</v>
       </c>
-      <c r="G58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2292,22 +2426,25 @@
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1200</v>
+        <v>1400</v>
       </c>
       <c r="E59" s="3">
-        <v>1200</v>
+        <v>1400</v>
       </c>
       <c r="F59" s="3">
         <v>1300</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>3</v>
+      <c r="G59" s="3">
+        <v>1500</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>3</v>
@@ -2327,22 +2464,25 @@
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>8700</v>
+        <v>3300</v>
       </c>
       <c r="E60" s="3">
-        <v>11300</v>
+        <v>9700</v>
       </c>
       <c r="F60" s="3">
-        <v>2400</v>
-      </c>
-      <c r="G60" s="3" t="s">
-        <v>3</v>
+        <v>12500</v>
+      </c>
+      <c r="G60" s="3">
+        <v>2700</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>3</v>
@@ -2362,22 +2502,25 @@
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E61" s="3">
         <v>100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>300</v>
       </c>
-      <c r="F61" s="3">
-        <v>6800</v>
-      </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="H61" s="3">
         <v>0</v>
@@ -2397,22 +2540,25 @@
       <c r="M61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>3000</v>
+        <v>3500</v>
       </c>
       <c r="E62" s="3">
-        <v>0</v>
+        <v>3400</v>
       </c>
       <c r="F62" s="3">
-        <v>6400</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="G62" s="3">
+        <v>7100</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>3</v>
@@ -2432,8 +2578,11 @@
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2467,8 +2616,11 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2502,8 +2654,11 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2537,22 +2692,25 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>11800</v>
+        <v>13900</v>
       </c>
       <c r="E66" s="3">
-        <v>11600</v>
+        <v>13200</v>
       </c>
       <c r="F66" s="3">
-        <v>15500</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>3</v>
+        <v>12900</v>
+      </c>
+      <c r="G66" s="3">
+        <v>17300</v>
       </c>
       <c r="H66" s="3" t="s">
         <v>3</v>
@@ -2572,8 +2730,11 @@
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2587,8 +2748,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2622,8 +2784,11 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2657,8 +2822,11 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2669,10 +2837,10 @@
         <v>0</v>
       </c>
       <c r="F70" s="3">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="G70" s="3">
-        <v>0</v>
+        <v>7700</v>
       </c>
       <c r="H70" s="3">
         <v>0</v>
@@ -2692,8 +2860,11 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2727,22 +2898,25 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-35300</v>
+        <v>-45100</v>
       </c>
       <c r="E72" s="3">
-        <v>-28000</v>
+        <v>-39300</v>
       </c>
       <c r="F72" s="3">
-        <v>-21100</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>3</v>
+        <v>-31100</v>
+      </c>
+      <c r="G72" s="3">
+        <v>-23400</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>3</v>
@@ -2762,8 +2936,11 @@
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2797,8 +2974,11 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2832,8 +3012,11 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2867,22 +3050,25 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>14200</v>
+        <v>10100</v>
       </c>
       <c r="E76" s="3">
-        <v>12100</v>
+        <v>15800</v>
       </c>
       <c r="F76" s="3">
-        <v>12100</v>
-      </c>
-      <c r="G76" s="3" t="s">
-        <v>3</v>
+        <v>13500</v>
+      </c>
+      <c r="G76" s="3">
+        <v>13400</v>
       </c>
       <c r="H76" s="3" t="s">
         <v>3</v>
@@ -2902,8 +3088,11 @@
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2937,34 +3126,37 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45412</v>
+      </c>
+      <c r="E80" s="2">
         <v>45230</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45046</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44865</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44681</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44500</v>
       </c>
-      <c r="I80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="J80" s="2" t="s">
         <v>3</v>
       </c>
@@ -2977,28 +3169,31 @@
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-7300</v>
+        <v>-14000</v>
       </c>
       <c r="E81" s="3">
-        <v>-12500</v>
+        <v>-8200</v>
       </c>
       <c r="F81" s="3">
-        <v>-5600</v>
+        <v>-14000</v>
       </c>
       <c r="G81" s="3">
-        <v>-7100</v>
+        <v>-6300</v>
       </c>
       <c r="H81" s="3">
-        <v>-4000</v>
-      </c>
-      <c r="I81" s="3" t="s">
-        <v>3</v>
+        <v>-7900</v>
+      </c>
+      <c r="I81" s="3">
+        <v>-4400</v>
       </c>
       <c r="J81" s="3" t="s">
         <v>3</v>
@@ -3012,8 +3207,11 @@
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3027,29 +3225,30 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>600</v>
+        <v>1300</v>
       </c>
       <c r="E83" s="3">
         <v>700</v>
       </c>
       <c r="F83" s="3">
+        <v>800</v>
+      </c>
+      <c r="G83" s="3">
+        <v>300</v>
+      </c>
+      <c r="H83" s="3">
+        <v>500</v>
+      </c>
+      <c r="I83" s="3">
         <v>200</v>
       </c>
-      <c r="G83" s="3">
-        <v>500</v>
-      </c>
-      <c r="H83" s="3">
-        <v>200</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3062,8 +3261,11 @@
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3097,8 +3299,11 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3132,8 +3337,11 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3167,8 +3375,11 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3202,8 +3413,11 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3237,28 +3451,31 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-8800</v>
+        <v>-14800</v>
       </c>
       <c r="E89" s="3">
-        <v>-11600</v>
+        <v>-9800</v>
       </c>
       <c r="F89" s="3">
-        <v>-5500</v>
+        <v>-12900</v>
       </c>
       <c r="G89" s="3">
-        <v>-6900</v>
+        <v>-6100</v>
       </c>
       <c r="H89" s="3">
-        <v>-4300</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
+        <v>-7600</v>
+      </c>
+      <c r="I89" s="3">
+        <v>-4800</v>
       </c>
       <c r="J89" s="3" t="s">
         <v>3</v>
@@ -3272,8 +3489,11 @@
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3287,26 +3507,27 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-115200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-68800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-40000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-49300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-12100</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
       <c r="I91" s="3">
         <v>0</v>
       </c>
@@ -3322,8 +3543,11 @@
       <c r="M91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3357,8 +3581,11 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3392,29 +3619,32 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F94" s="3">
+        <v>-600</v>
+      </c>
+      <c r="G94" s="3">
         <v>-400</v>
       </c>
-      <c r="E94" s="3">
-        <v>-600</v>
-      </c>
-      <c r="F94" s="3">
-        <v>-300</v>
-      </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-400</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J94" s="3" t="s">
         <v>3</v>
       </c>
@@ -3427,8 +3657,11 @@
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3442,8 +3675,9 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3477,8 +3711,11 @@
       <c r="M96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3512,8 +3749,11 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3547,8 +3787,11 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3582,28 +3825,31 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>10800</v>
+        <v>12200</v>
       </c>
       <c r="E100" s="3">
-        <v>14300</v>
+        <v>12100</v>
       </c>
       <c r="F100" s="3">
-        <v>15200</v>
+        <v>15900</v>
       </c>
       <c r="G100" s="3">
-        <v>-800</v>
+        <v>17000</v>
       </c>
       <c r="H100" s="3">
-        <v>1500</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
+        <v>-900</v>
+      </c>
+      <c r="I100" s="3">
+        <v>1600</v>
       </c>
       <c r="J100" s="3" t="s">
         <v>3</v>
@@ -3617,17 +3863,20 @@
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>200</v>
+      </c>
+      <c r="E101" s="3">
         <v>300</v>
       </c>
-      <c r="E101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F101" s="3" t="s">
         <v>3</v>
       </c>
@@ -3643,8 +3892,8 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -3652,28 +3901,31 @@
       <c r="M101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>1800</v>
+        <v>-3700</v>
       </c>
       <c r="E102" s="3">
-        <v>2200</v>
+        <v>2000</v>
       </c>
       <c r="F102" s="3">
-        <v>9400</v>
+        <v>2400</v>
       </c>
       <c r="G102" s="3">
-        <v>-8100</v>
+        <v>10500</v>
       </c>
       <c r="H102" s="3">
-        <v>-3300</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>3</v>
+        <v>-9000</v>
+      </c>
+      <c r="I102" s="3">
+        <v>-3600</v>
       </c>
       <c r="J102" s="3" t="s">
         <v>3</v>
@@ -3685,6 +3937,9 @@
         <v>3</v>
       </c>
       <c r="M102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
